--- a/test-cases/Vitalis_Test_Cases.xlsx
+++ b/test-cases/Vitalis_Test_Cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\软件测试\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\软件测试\Vitalis测试项目\test-cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BE95543-8298-41F5-8D44-C9C0C5B9A9F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F78E57D-35FE-48DF-9B59-2B0F7A33FD92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="1037">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1858" uniqueCount="1053">
   <si>
     <t>用例标题</t>
   </si>
@@ -1849,10 +1849,6 @@
     <t>系统</t>
   </si>
   <si>
-    <t>1.已登录
-2.有记录</t>
-  </si>
-  <si>
     <t>列表和统计重新加载</t>
   </si>
   <si>
@@ -1866,14 +1862,6 @@
   </si>
   <si>
     <t>SYS-003</t>
-  </si>
-  <si>
-    <t>1.已登录
-2.使用演示账号</t>
-  </si>
-  <si>
-    <t>1.点击"退出登录"
-2.查看登录表单</t>
   </si>
   <si>
     <t>REG-036</t>
@@ -2995,12 +2983,6 @@
     <t>跑步 80</t>
   </si>
   <si>
-    <t>1.输入合法运动类型和卡路里数，选择合法日期
-2.点击添加运动
-2.查看各输入框</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>今日消耗统计正确（多条记录）</t>
   </si>
   <si>
@@ -3019,10 +3001,6 @@
   </si>
   <si>
     <t>今日消耗统计正确（0条记录）</t>
-  </si>
-  <si>
-    <t>1.不添加任何运动记录
-4.查看今日消耗</t>
   </si>
   <si>
     <t>今日消耗显示0，统计正确</t>
@@ -3643,12 +3621,6 @@
     <t>显示⚖️一般级建议，热量盈余/缺口偏大</t>
   </si>
   <si>
-    <t>退出登录后登录表单保留演示账号信息（预置账号留存）</t>
-  </si>
-  <si>
-    <t>登录表单保留演示账号，手机号显示13800138000，密码显示demo123</t>
-  </si>
-  <si>
     <t>用户名：test
 手机号：13912345693
 密码：ab123
@@ -3803,6 +3775,103 @@
   </si>
   <si>
     <t>日均净值800</t>
+  </si>
+  <si>
+    <t>SYS-005</t>
+  </si>
+  <si>
+    <t>SYS-006</t>
+  </si>
+  <si>
+    <t>SYS-007</t>
+  </si>
+  <si>
+    <t>SYS-004</t>
+  </si>
+  <si>
+    <t>P1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.输入合法运动类型和卡路里数，选择合法日期
+2.点击添加运动
+3.查看各输入框</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.不添加任何运动记录
+2.查看今日消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>页面在Chrome浏览器正常显示（布局无错乱）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>页面在IE浏览器正常显示（布局无错乱）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>页面在Safari浏览器正常显示（布局无错乱）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>页面在Firefox浏览器正常显示（布局无错乱）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SYS-008</t>
+  </si>
+  <si>
+    <t>1.已登录
+2.有记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.已登录
+2.使用Chrome 浏览器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.已登录
+2.使用Edge 浏览器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.已登录
+2.使用Safari 浏览器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.已登录
+2.使用Firefox 浏览器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查看各模块布局、文字、按钮控件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>页面在Win11操作系统正常显示（布局无错乱）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.已登录
+2.使用Win11操作系统</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有模块布局正常，文字无重叠，按钮可点击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>页面在iOS17操作系统正常显示（布局无错乱）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.已登录
+2.使用iOS17操作系统</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4316,7 +4385,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:T201"/>
+  <dimension ref="A1:T206"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -4333,7 +4402,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="15.75" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -4377,13 +4446,13 @@
         <v>12</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>14</v>
@@ -4417,13 +4486,13 @@
         <v>12</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>14</v>
@@ -4457,13 +4526,13 @@
         <v>20</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>14</v>
@@ -4497,13 +4566,13 @@
         <v>20</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>14</v>
@@ -4537,13 +4606,13 @@
         <v>20</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>14</v>
@@ -4577,13 +4646,13 @@
         <v>20</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>14</v>
@@ -4617,13 +4686,13 @@
         <v>20</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>14</v>
@@ -4657,13 +4726,13 @@
         <v>20</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>14</v>
@@ -4688,7 +4757,7 @@
         <v>31</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>11</v>
@@ -4697,13 +4766,13 @@
         <v>20</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>14</v>
@@ -4728,7 +4797,7 @@
         <v>32</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>11</v>
@@ -4737,13 +4806,13 @@
         <v>20</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>14</v>
@@ -4768,7 +4837,7 @@
         <v>33</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>11</v>
@@ -4777,13 +4846,13 @@
         <v>20</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>14</v>
@@ -4808,7 +4877,7 @@
         <v>34</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>11</v>
@@ -4817,13 +4886,13 @@
         <v>20</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>14</v>
@@ -4848,7 +4917,7 @@
         <v>35</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>11</v>
@@ -4857,13 +4926,13 @@
         <v>20</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>14</v>
@@ -4888,7 +4957,7 @@
         <v>38</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>11</v>
@@ -4897,13 +4966,13 @@
         <v>20</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>14</v>
@@ -4928,7 +4997,7 @@
         <v>40</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>11</v>
@@ -4937,13 +5006,13 @@
         <v>20</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>14</v>
@@ -4977,13 +5046,13 @@
         <v>20</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>37</v>
@@ -5017,13 +5086,13 @@
         <v>20</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>37</v>
@@ -5057,13 +5126,13 @@
         <v>20</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>37</v>
@@ -5088,7 +5157,7 @@
         <v>48</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>11</v>
@@ -5097,19 +5166,19 @@
         <v>20</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="J20" s="5"/>
       <c r="K20" s="1"/>
@@ -5137,13 +5206,13 @@
         <v>20</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>47</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>44</v>
@@ -5177,13 +5246,13 @@
         <v>20</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>50</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>44</v>
@@ -5217,13 +5286,13 @@
         <v>20</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>53</v>
@@ -5257,13 +5326,13 @@
         <v>20</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>53</v>
@@ -5297,13 +5366,13 @@
         <v>20</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>990</v>
+        <v>983</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>53</v>
@@ -5337,13 +5406,13 @@
         <v>20</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>53</v>
@@ -5377,13 +5446,13 @@
         <v>12</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>62</v>
@@ -5417,13 +5486,13 @@
         <v>20</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>65</v>
@@ -5457,13 +5526,13 @@
         <v>20</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>68</v>
@@ -5497,13 +5566,13 @@
         <v>71</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>68</v>
@@ -5537,13 +5606,13 @@
         <v>71</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>68</v>
@@ -5568,7 +5637,7 @@
         <v>91</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>11</v>
@@ -5577,16 +5646,16 @@
         <v>20</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="I32" s="4" t="s">
         <v>15</v>
@@ -5608,7 +5677,7 @@
         <v>99</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>11</v>
@@ -5617,16 +5686,16 @@
         <v>20</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="I33" s="4" t="s">
         <v>15</v>
@@ -5648,7 +5717,7 @@
         <v>108</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>11</v>
@@ -5657,16 +5726,16 @@
         <v>71</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="I34" s="4" t="s">
         <v>15</v>
@@ -5688,7 +5757,7 @@
         <v>116</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>11</v>
@@ -5700,13 +5769,13 @@
         <v>13</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="I35" s="4" t="s">
         <v>15</v>
@@ -5728,7 +5797,7 @@
         <v>117</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>11</v>
@@ -5740,13 +5809,13 @@
         <v>13</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>15</v>
@@ -5765,10 +5834,10 @@
     </row>
     <row r="37" spans="1:20" ht="124.9" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>11</v>
@@ -5777,16 +5846,16 @@
         <v>93</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>15</v>
@@ -5805,10 +5874,10 @@
     </row>
     <row r="38" spans="1:20" ht="27.75" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>75</v>
@@ -5835,7 +5904,7 @@
     </row>
     <row r="39" spans="1:20" ht="27.75" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>83</v>
@@ -5865,10 +5934,10 @@
     </row>
     <row r="40" spans="1:20" ht="27.75" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>92</v>
@@ -5895,7 +5964,7 @@
     </row>
     <row r="41" spans="1:20" ht="27.75" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>100</v>
@@ -5925,10 +5994,10 @@
     </row>
     <row r="42" spans="1:20" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>109</v>
@@ -5958,7 +6027,7 @@
         <v>118</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>119</v>
@@ -5967,13 +6036,13 @@
         <v>12</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="H43" s="5" t="s">
         <v>120</v>
@@ -5998,7 +6067,7 @@
         <v>121</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>119</v>
@@ -6007,13 +6076,13 @@
         <v>20</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="F44" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="G44" s="5" t="s">
         <v>641</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>644</v>
       </c>
       <c r="H44" s="5" t="s">
         <v>122</v>
@@ -6047,13 +6116,13 @@
         <v>20</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="H45" s="5" t="s">
         <v>128</v>
@@ -6087,13 +6156,13 @@
         <v>20</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="H46" s="5" t="s">
         <v>122</v>
@@ -6127,13 +6196,13 @@
         <v>20</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="H47" s="5" t="s">
         <v>128</v>
@@ -6158,7 +6227,7 @@
         <v>131</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>119</v>
@@ -6170,13 +6239,13 @@
         <v>125</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>15</v>
@@ -6195,10 +6264,10 @@
     </row>
     <row r="49" spans="1:20" ht="55.5" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>119</v>
@@ -6207,16 +6276,16 @@
         <v>20</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>15</v>
@@ -6235,10 +6304,10 @@
     </row>
     <row r="50" spans="1:20" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>119</v>
@@ -6250,13 +6319,13 @@
         <v>125</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="I50" s="4" t="s">
         <v>15</v>
@@ -6275,10 +6344,10 @@
     </row>
     <row r="51" spans="1:20" ht="55.5" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>119</v>
@@ -6290,13 +6359,13 @@
         <v>125</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>15</v>
@@ -6315,10 +6384,10 @@
     </row>
     <row r="52" spans="1:20" ht="69.400000000000006" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>119</v>
@@ -6327,16 +6396,16 @@
         <v>93</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>15</v>
@@ -6358,7 +6427,7 @@
         <v>132</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>133</v>
@@ -6367,7 +6436,7 @@
         <v>134</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>136</v>
@@ -6397,7 +6466,7 @@
         <v>143</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>145</v>
@@ -6427,7 +6496,7 @@
         <v>152</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>153</v>
@@ -6457,7 +6526,7 @@
         <v>160</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>161</v>
@@ -6487,13 +6556,13 @@
         <v>168</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F57" s="6" t="s">
         <v>169</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>170</v>
@@ -6508,7 +6577,7 @@
         <v>172</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>173</v>
@@ -6517,7 +6586,7 @@
         <v>174</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>175</v>
@@ -6538,7 +6607,7 @@
         <v>179</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="C59" s="7" t="s">
         <v>180</v>
@@ -6547,13 +6616,13 @@
         <v>181</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F59" s="6" t="s">
         <v>182</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H59" s="6" t="s">
         <v>183</v>
@@ -6568,7 +6637,7 @@
         <v>185</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>133</v>
@@ -6577,13 +6646,13 @@
         <v>20</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>136</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="H60" s="6" t="s">
         <v>163</v>
@@ -6598,7 +6667,7 @@
         <v>192</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>186</v>
@@ -6607,7 +6676,7 @@
         <v>187</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F61" s="6" t="s">
         <v>188</v>
@@ -6628,7 +6697,7 @@
         <v>198</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>193</v>
@@ -6637,13 +6706,13 @@
         <v>194</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>195</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>196</v>
@@ -6658,7 +6727,7 @@
         <v>205</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>133</v>
@@ -6667,13 +6736,13 @@
         <v>20</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F63" s="6" t="s">
         <v>136</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>163</v>
@@ -6688,7 +6757,7 @@
         <v>206</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="C64" s="7" t="s">
         <v>270</v>
@@ -6697,7 +6766,7 @@
         <v>271</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>272</v>
@@ -6706,10 +6775,10 @@
         <v>273</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="I64" s="7" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="J64" s="7"/>
     </row>
@@ -6727,13 +6796,13 @@
         <v>201</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F65" s="6" t="s">
         <v>202</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="H65" s="6" t="s">
         <v>203</v>
@@ -6757,13 +6826,13 @@
         <v>210</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>211</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="H66" s="6" t="s">
         <v>212</v>
@@ -6787,7 +6856,7 @@
         <v>217</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F67" s="6" t="s">
         <v>136</v>
@@ -6817,7 +6886,7 @@
         <v>224</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>136</v>
@@ -6847,7 +6916,7 @@
         <v>231</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F69" s="6" t="s">
         <v>136</v>
@@ -6877,7 +6946,7 @@
         <v>238</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>136</v>
@@ -6895,28 +6964,28 @@
     </row>
     <row r="71" spans="1:10" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A71" s="7" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="D71" s="7" t="s">
         <v>71</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="G71" s="6" t="s">
+        <v>774</v>
+      </c>
+      <c r="H71" s="6" t="s">
         <v>777</v>
-      </c>
-      <c r="H71" s="6" t="s">
-        <v>780</v>
       </c>
       <c r="I71" s="7" t="s">
         <v>15</v>
@@ -6937,13 +7006,13 @@
         <v>245</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>246</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>247</v>
@@ -6967,7 +7036,7 @@
         <v>252</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F73" s="6" t="s">
         <v>136</v>
@@ -6997,7 +7066,7 @@
         <v>259</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>136</v>
@@ -7027,13 +7096,13 @@
         <v>266</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F75" s="6" t="s">
         <v>136</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>267</v>
@@ -7057,7 +7126,7 @@
         <v>277</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>136</v>
@@ -7087,13 +7156,13 @@
         <v>284</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F77" s="6" t="s">
         <v>136</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>285</v>
@@ -7108,7 +7177,7 @@
         <v>287</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="C78" s="7" t="s">
         <v>133</v>
@@ -7117,19 +7186,19 @@
         <v>20</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="I78" s="8" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="J78" s="7"/>
     </row>
@@ -7138,7 +7207,7 @@
         <v>288</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="C79" s="7" t="s">
         <v>289</v>
@@ -7147,16 +7216,16 @@
         <v>290</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="I79" s="7" t="s">
         <v>291</v>
@@ -7168,7 +7237,7 @@
         <v>292</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="C80" s="7" t="s">
         <v>293</v>
@@ -7177,13 +7246,13 @@
         <v>294</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>295</v>
@@ -7198,7 +7267,7 @@
         <v>297</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="C81" s="7" t="s">
         <v>299</v>
@@ -7207,22 +7276,22 @@
         <v>300</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="I81" s="9" t="s">
         <v>301</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="41.65" x14ac:dyDescent="0.35">
@@ -7230,7 +7299,7 @@
         <v>298</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="C82" s="7" t="s">
         <v>303</v>
@@ -7242,13 +7311,13 @@
         <v>305</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="I82" s="7" t="s">
         <v>306</v>
@@ -7260,7 +7329,7 @@
         <v>302</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="C83" s="7" t="s">
         <v>133</v>
@@ -7272,13 +7341,13 @@
         <v>144</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="I83" s="7" t="s">
         <v>15</v>
@@ -7290,7 +7359,7 @@
         <v>307</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="C84" s="7" t="s">
         <v>133</v>
@@ -7302,13 +7371,13 @@
         <v>144</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="I84" s="7" t="s">
         <v>15</v>
@@ -7320,7 +7389,7 @@
         <v>308</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="C85" s="7" t="s">
         <v>309</v>
@@ -7329,13 +7398,13 @@
         <v>310</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="F85" s="6" t="s">
         <v>311</v>
       </c>
       <c r="G85" s="6" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="H85" s="6" t="s">
         <v>312</v>
@@ -7350,7 +7419,7 @@
         <v>314</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="C86" s="7" t="s">
         <v>315</v>
@@ -7368,7 +7437,7 @@
         <v>319</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="I86" s="7" t="s">
         <v>320</v>
@@ -7380,7 +7449,7 @@
         <v>321</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="C87" s="7" t="s">
         <v>322</v>
@@ -7389,7 +7458,7 @@
         <v>323</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="F87" s="6" t="s">
         <v>324</v>
@@ -7410,7 +7479,7 @@
         <v>328</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="C88" s="7" t="s">
         <v>329</v>
@@ -7419,7 +7488,7 @@
         <v>330</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>331</v>
@@ -7440,7 +7509,7 @@
         <v>335</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="C89" s="7" t="s">
         <v>336</v>
@@ -7512,10 +7581,10 @@
         <v>135</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="G91" s="6" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="H91" s="6" t="s">
         <v>355</v>
@@ -7530,22 +7599,22 @@
         <v>357</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="D92" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="H92" s="6" t="s">
         <v>163</v>
@@ -7560,22 +7629,22 @@
         <v>358</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="D93" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="H93" s="6" t="s">
         <v>163</v>
@@ -7590,22 +7659,22 @@
         <v>359</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="D94" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F94" s="6" t="s">
+        <v>760</v>
+      </c>
+      <c r="G94" s="6" t="s">
         <v>763</v>
-      </c>
-      <c r="G94" s="6" t="s">
-        <v>766</v>
       </c>
       <c r="H94" s="6" t="s">
         <v>163</v>
@@ -7620,22 +7689,22 @@
         <v>365</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="D95" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="H95" s="6" t="s">
         <v>163</v>
@@ -7650,25 +7719,25 @@
         <v>372</v>
       </c>
       <c r="B96" s="6" t="s">
+        <v>835</v>
+      </c>
+      <c r="C96" s="7" t="s">
         <v>840</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>845</v>
       </c>
       <c r="D96" s="7" t="s">
         <v>71</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="I96" s="7" t="s">
         <v>15</v>
@@ -7680,22 +7749,22 @@
         <v>379</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="D97" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F97" s="6" t="s">
         <v>339</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="H97" s="6" t="s">
         <v>163</v>
@@ -7710,22 +7779,22 @@
         <v>386</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="D98" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="H98" s="6" t="s">
         <v>163</v>
@@ -7740,22 +7809,22 @@
         <v>393</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="D99" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="G99" s="6" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="H99" s="6" t="s">
         <v>163</v>
@@ -7770,22 +7839,22 @@
         <v>394</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="D100" s="7" t="s">
         <v>20</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="H100" s="6" t="s">
         <v>163</v>
@@ -7800,28 +7869,28 @@
         <v>402</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="D101" s="7" t="s">
         <v>71</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="G101" s="6" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>991</v>
+        <v>984</v>
       </c>
       <c r="I101" s="7" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="J101" s="7"/>
     </row>
@@ -7833,7 +7902,7 @@
         <v>360</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="D102" s="7" t="s">
         <v>361</v>
@@ -7842,7 +7911,7 @@
         <v>135</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="G102" s="6" t="s">
         <v>362</v>
@@ -7875,7 +7944,7 @@
         <v>369</v>
       </c>
       <c r="G103" s="6" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="H103" s="6" t="s">
         <v>370</v>
@@ -7902,7 +7971,7 @@
         <v>135</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="G104" s="6" t="s">
         <v>376</v>
@@ -7932,7 +8001,7 @@
         <v>135</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="G105" s="6" t="s">
         <v>383</v>
@@ -7950,7 +8019,7 @@
         <v>429</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="C106" s="7" t="s">
         <v>336</v>
@@ -7959,13 +8028,13 @@
         <v>71</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>339</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="H106" s="6" t="s">
         <v>219</v>
@@ -7992,7 +8061,7 @@
         <v>135</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="G107" s="6" t="s">
         <v>390</v>
@@ -8007,7 +8076,7 @@
     </row>
     <row r="108" spans="1:10" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A108" s="7" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>395</v>
@@ -8037,7 +8106,7 @@
     </row>
     <row r="109" spans="1:10" ht="55.5" x14ac:dyDescent="0.35">
       <c r="A109" s="7" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>403</v>
@@ -8052,7 +8121,7 @@
         <v>135</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="G109" s="6" t="s">
         <v>406</v>
@@ -8067,7 +8136,7 @@
     </row>
     <row r="110" spans="1:10" ht="55.5" x14ac:dyDescent="0.35">
       <c r="A110" s="7" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>410</v>
@@ -8082,7 +8151,7 @@
         <v>135</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="G110" s="6" t="s">
         <v>413</v>
@@ -8097,10 +8166,10 @@
     </row>
     <row r="111" spans="1:10" ht="55.5" x14ac:dyDescent="0.35">
       <c r="A111" s="7" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="C111" s="7" t="s">
         <v>336</v>
@@ -8109,13 +8178,13 @@
         <v>71</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F111" s="6" t="s">
         <v>339</v>
       </c>
       <c r="G111" s="6" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="H111" s="6" t="s">
         <v>261</v>
@@ -8127,10 +8196,10 @@
     </row>
     <row r="112" spans="1:10" ht="55.5" x14ac:dyDescent="0.35">
       <c r="A112" s="7" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="C112" s="7" t="s">
         <v>336</v>
@@ -8139,13 +8208,13 @@
         <v>71</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>339</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="H112" s="6" t="s">
         <v>247</v>
@@ -8157,7 +8226,7 @@
     </row>
     <row r="113" spans="1:10" ht="55.5" x14ac:dyDescent="0.35">
       <c r="A113" s="7" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>418</v>
@@ -8172,7 +8241,7 @@
         <v>421</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="G113" s="6" t="s">
         <v>422</v>
@@ -8187,10 +8256,10 @@
     </row>
     <row r="114" spans="1:10" ht="55.5" x14ac:dyDescent="0.35">
       <c r="A114" s="7" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C114" s="7" t="s">
         <v>336</v>
@@ -8199,28 +8268,28 @@
         <v>20</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="I114" s="8" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="J114" s="7"/>
     </row>
     <row r="115" spans="1:10" ht="55.5" x14ac:dyDescent="0.35">
       <c r="A115" s="7" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="C115" s="7" t="s">
         <v>336</v>
@@ -8229,16 +8298,16 @@
         <v>20</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="G115" s="6" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="H115" s="6" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="I115" s="7" t="s">
         <v>15</v>
@@ -8247,10 +8316,10 @@
     </row>
     <row r="116" spans="1:10" ht="55.5" x14ac:dyDescent="0.35">
       <c r="A116" s="7" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="C116" s="7" t="s">
         <v>336</v>
@@ -8259,13 +8328,13 @@
         <v>71</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>803</v>
+        <v>1035</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="H116" s="6" t="s">
         <v>295</v>
@@ -8277,10 +8346,10 @@
     </row>
     <row r="117" spans="1:10" ht="55.5" x14ac:dyDescent="0.35">
       <c r="A117" s="7" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="C117" s="7" t="s">
         <v>336</v>
@@ -8289,30 +8358,30 @@
         <v>71</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="G117" s="6" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="H117" s="6" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="I117" s="9" t="s">
         <v>301</v>
       </c>
       <c r="J117" s="7" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A118" s="7" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="C118" s="7" t="s">
         <v>336</v>
@@ -8324,13 +8393,13 @@
         <v>144</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="I118" s="7" t="s">
         <v>15</v>
@@ -8339,10 +8408,10 @@
     </row>
     <row r="119" spans="1:10" ht="27.75" x14ac:dyDescent="0.35">
       <c r="A119" s="7" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="C119" s="7" t="s">
         <v>336</v>
@@ -8354,13 +8423,13 @@
         <v>144</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="G119" s="6" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="H119" s="6" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="I119" s="7" t="s">
         <v>15</v>
@@ -8369,10 +8438,10 @@
     </row>
     <row r="120" spans="1:10" ht="27.75" x14ac:dyDescent="0.35">
       <c r="A120" s="7" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="C120" s="7" t="s">
         <v>336</v>
@@ -8384,13 +8453,13 @@
         <v>144</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>810</v>
+        <v>1036</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="I120" s="7" t="s">
         <v>15</v>
@@ -8399,10 +8468,10 @@
     </row>
     <row r="121" spans="1:10" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A121" s="7" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="C121" s="7" t="s">
         <v>426</v>
@@ -8411,13 +8480,13 @@
         <v>427</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="G121" s="6" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="H121" s="6" t="s">
         <v>312</v>
@@ -8429,13 +8498,13 @@
     </row>
     <row r="122" spans="1:10" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A122" s="7" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="D122" s="7" t="s">
         <v>71</v>
@@ -8444,13 +8513,13 @@
         <v>144</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="G122" s="6" t="s">
         <v>319</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="I122" s="7" t="s">
         <v>15</v>
@@ -8459,10 +8528,10 @@
     </row>
     <row r="123" spans="1:10" ht="27.75" x14ac:dyDescent="0.35">
       <c r="A123" s="7" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="C123" s="7" t="s">
         <v>430</v>
@@ -8471,7 +8540,7 @@
         <v>431</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="F123" s="6" t="s">
         <v>432</v>
@@ -8489,10 +8558,10 @@
     </row>
     <row r="124" spans="1:10" ht="27.75" x14ac:dyDescent="0.35">
       <c r="A124" s="7" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="C124" s="7" t="s">
         <v>437</v>
@@ -8501,7 +8570,7 @@
         <v>438</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>439</v>
@@ -8522,7 +8591,7 @@
         <v>443</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>444</v>
@@ -8534,7 +8603,7 @@
         <v>445</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="G125" s="5" t="s">
         <v>446</v>
@@ -8552,7 +8621,7 @@
         <v>448</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>444</v>
@@ -8582,7 +8651,7 @@
         <v>452</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>444</v>
@@ -8614,7 +8683,7 @@
         <v>456</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>444</v>
@@ -8644,7 +8713,7 @@
         <v>460</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>444</v>
@@ -8656,7 +8725,7 @@
         <v>461</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="G129" s="5" t="s">
         <v>462</v>
@@ -8674,7 +8743,7 @@
         <v>464</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>465</v>
@@ -8701,10 +8770,10 @@
     </row>
     <row r="131" spans="1:20" s="3" customFormat="1" ht="27.75" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>465</v>
@@ -8734,7 +8803,7 @@
         <v>469</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>465</v>
@@ -8764,7 +8833,7 @@
         <v>471</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>465</v>
@@ -8794,7 +8863,7 @@
         <v>474</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>465</v>
@@ -8806,7 +8875,7 @@
         <v>468</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="G134" s="5" t="s">
         <v>472</v>
@@ -8824,7 +8893,7 @@
         <v>477</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>465</v>
@@ -8836,7 +8905,7 @@
         <v>468</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="G135" s="5" t="s">
         <v>484</v>
@@ -8854,7 +8923,7 @@
         <v>481</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>465</v>
@@ -8866,13 +8935,13 @@
         <v>468</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="H136" s="5" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="I136" s="4" t="s">
         <v>15</v>
@@ -8894,7 +8963,7 @@
         <v>483</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>465</v>
@@ -8906,7 +8975,7 @@
         <v>468</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="G137" s="5" t="s">
         <v>487</v>
@@ -8924,7 +8993,7 @@
         <v>486</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>465</v>
@@ -8936,13 +9005,13 @@
         <v>468</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="H138" s="5" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="I138" s="4" t="s">
         <v>15</v>
@@ -8964,7 +9033,7 @@
         <v>489</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>465</v>
@@ -8976,13 +9045,13 @@
         <v>468</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="G139" s="5" t="s">
         <v>470</v>
       </c>
       <c r="H139" s="5" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="I139" s="4" t="s">
         <v>15</v>
@@ -9004,7 +9073,7 @@
         <v>492</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>465</v>
@@ -9016,7 +9085,7 @@
         <v>468</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="G140" s="5" t="s">
         <v>490</v>
@@ -9034,7 +9103,7 @@
         <v>494</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>465</v>
@@ -9046,7 +9115,7 @@
         <v>468</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="G141" s="5" t="s">
         <v>493</v>
@@ -9064,7 +9133,7 @@
         <v>497</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>465</v>
@@ -9076,7 +9145,7 @@
         <v>468</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="G142" s="5" t="s">
         <v>495</v>
@@ -9094,7 +9163,7 @@
         <v>500</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>465</v>
@@ -9106,10 +9175,10 @@
         <v>468</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="H143" s="5" t="s">
         <v>491</v>
@@ -9134,7 +9203,7 @@
         <v>502</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>465</v>
@@ -9146,10 +9215,10 @@
         <v>468</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="H144" s="5" t="s">
         <v>491</v>
@@ -9174,7 +9243,7 @@
         <v>503</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>465</v>
@@ -9186,10 +9255,10 @@
         <v>468</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="H145" s="5" t="s">
         <v>496</v>
@@ -9214,7 +9283,7 @@
         <v>504</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>465</v>
@@ -9226,7 +9295,7 @@
         <v>498</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="G146" s="5" t="s">
         <v>79</v>
@@ -9244,7 +9313,7 @@
         <v>507</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>465</v>
@@ -9256,7 +9325,7 @@
         <v>498</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="G147" s="5" t="s">
         <v>79</v>
@@ -9271,10 +9340,10 @@
     </row>
     <row r="148" spans="1:20" s="3" customFormat="1" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>465</v>
@@ -9286,7 +9355,7 @@
         <v>498</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="G148" s="5" t="s">
         <v>79</v>
@@ -9301,10 +9370,10 @@
     </row>
     <row r="149" spans="1:20" s="3" customFormat="1" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="C149" s="4" t="s">
         <v>465</v>
@@ -9316,7 +9385,7 @@
         <v>498</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="G149" s="5" t="s">
         <v>79</v>
@@ -9331,10 +9400,10 @@
     </row>
     <row r="150" spans="1:20" s="3" customFormat="1" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>465</v>
@@ -9352,7 +9421,7 @@
         <v>79</v>
       </c>
       <c r="H150" s="5" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="I150" s="4" t="s">
         <v>15</v>
@@ -9361,10 +9430,10 @@
     </row>
     <row r="151" spans="1:20" s="3" customFormat="1" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>465</v>
@@ -9376,13 +9445,13 @@
         <v>508</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="G151" s="5" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="H151" s="5" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="I151" s="4" t="s">
         <v>15</v>
@@ -9406,7 +9475,7 @@
         <v>512</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G152" s="5" t="s">
         <v>513</v>
@@ -9436,7 +9505,7 @@
         <v>517</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="G153" s="5" t="s">
         <v>518</v>
@@ -9466,7 +9535,7 @@
         <v>522</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G154" s="5" t="s">
         <v>523</v>
@@ -9484,7 +9553,7 @@
         <v>525</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="C155" s="4" t="s">
         <v>511</v>
@@ -9514,7 +9583,7 @@
         <v>529</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>511</v>
@@ -9523,7 +9592,7 @@
         <v>20</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="F156" s="5" t="s">
         <v>527</v>
@@ -9544,7 +9613,7 @@
         <v>531</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>511</v>
@@ -9553,16 +9622,16 @@
         <v>20</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="G157" s="5" t="s">
         <v>532</v>
       </c>
       <c r="H157" s="5" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="I157" s="4" t="s">
         <v>15</v>
@@ -9574,7 +9643,7 @@
         <v>533</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>511</v>
@@ -9583,16 +9652,16 @@
         <v>20</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="G158" s="5" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="H158" s="5" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="I158" s="4" t="s">
         <v>15</v>
@@ -9604,7 +9673,7 @@
         <v>534</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>511</v>
@@ -9616,10 +9685,10 @@
         <v>537</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G159" s="5" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="H159" s="5" t="s">
         <v>535</v>
@@ -9634,7 +9703,7 @@
         <v>536</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>511</v>
@@ -9646,10 +9715,10 @@
         <v>537</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="H160" s="5" t="s">
         <v>535</v>
@@ -9664,7 +9733,7 @@
         <v>539</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>511</v>
@@ -9676,10 +9745,10 @@
         <v>537</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
       <c r="H161" s="5" t="s">
         <v>538</v>
@@ -9694,7 +9763,7 @@
         <v>540</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>511</v>
@@ -9706,10 +9775,10 @@
         <v>537</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G162" s="5" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="H162" s="5" t="s">
         <v>538</v>
@@ -9724,7 +9793,7 @@
         <v>542</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>511</v>
@@ -9736,10 +9805,10 @@
         <v>537</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="H163" s="5" t="s">
         <v>538</v>
@@ -9754,7 +9823,7 @@
         <v>544</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>511</v>
@@ -9766,13 +9835,13 @@
         <v>537</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="H164" s="5" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="I164" s="4" t="s">
         <v>15</v>
@@ -9784,7 +9853,7 @@
         <v>546</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>997</v>
+        <v>990</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>511</v>
@@ -9796,13 +9865,13 @@
         <v>537</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="H165" s="5" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="I165" s="4" t="s">
         <v>15</v>
@@ -9814,7 +9883,7 @@
         <v>547</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>511</v>
@@ -9826,13 +9895,13 @@
         <v>537</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G166" s="5" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="H166" s="5" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="I166" s="4" t="s">
         <v>15</v>
@@ -9844,7 +9913,7 @@
         <v>549</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>511</v>
@@ -9856,10 +9925,10 @@
         <v>537</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="H167" s="5" t="s">
         <v>541</v>
@@ -9874,7 +9943,7 @@
         <v>550</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>998</v>
+        <v>991</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>511</v>
@@ -9886,10 +9955,10 @@
         <v>537</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="H168" s="5" t="s">
         <v>541</v>
@@ -9904,7 +9973,7 @@
         <v>551</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>511</v>
@@ -9916,10 +9985,10 @@
         <v>537</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G169" s="5" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="H169" s="5" t="s">
         <v>541</v>
@@ -9934,7 +10003,7 @@
         <v>552</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>511</v>
@@ -9946,10 +10015,10 @@
         <v>537</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="H170" s="5" t="s">
         <v>543</v>
@@ -9964,7 +10033,7 @@
         <v>555</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>511</v>
@@ -9976,10 +10045,10 @@
         <v>537</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G171" s="5" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="H171" s="5" t="s">
         <v>543</v>
@@ -9994,7 +10063,7 @@
         <v>558</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>1001</v>
+        <v>994</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>511</v>
@@ -10006,13 +10075,13 @@
         <v>545</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G172" s="5" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="H172" s="5" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="I172" s="4" t="s">
         <v>15</v>
@@ -10021,10 +10090,10 @@
     </row>
     <row r="173" spans="1:10" s="3" customFormat="1" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>1002</v>
+        <v>995</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>511</v>
@@ -10036,13 +10105,13 @@
         <v>545</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="H173" s="5" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="I173" s="4" t="s">
         <v>15</v>
@@ -10051,10 +10120,10 @@
     </row>
     <row r="174" spans="1:10" s="3" customFormat="1" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>1003</v>
+        <v>996</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>511</v>
@@ -10066,13 +10135,13 @@
         <v>545</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G174" s="5" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="H174" s="5" t="s">
-        <v>968</v>
+        <v>963</v>
       </c>
       <c r="I174" s="4" t="s">
         <v>15</v>
@@ -10081,10 +10150,10 @@
     </row>
     <row r="175" spans="1:10" s="3" customFormat="1" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>1004</v>
+        <v>997</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>511</v>
@@ -10096,13 +10165,13 @@
         <v>545</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="H175" s="5" t="s">
-        <v>968</v>
+        <v>963</v>
       </c>
       <c r="I175" s="4" t="s">
         <v>15</v>
@@ -10111,10 +10180,10 @@
     </row>
     <row r="176" spans="1:10" s="3" customFormat="1" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>1005</v>
+        <v>998</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>511</v>
@@ -10126,13 +10195,13 @@
         <v>545</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G176" s="5" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="H176" s="5" t="s">
-        <v>968</v>
+        <v>963</v>
       </c>
       <c r="I176" s="4" t="s">
         <v>15</v>
@@ -10141,10 +10210,10 @@
     </row>
     <row r="177" spans="1:10" s="3" customFormat="1" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
       <c r="C177" s="4" t="s">
         <v>511</v>
@@ -10156,13 +10225,13 @@
         <v>545</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G177" s="5" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="H177" s="5" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="I177" s="4" t="s">
         <v>15</v>
@@ -10171,10 +10240,10 @@
     </row>
     <row r="178" spans="1:10" s="3" customFormat="1" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>1007</v>
+        <v>1000</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>511</v>
@@ -10186,13 +10255,13 @@
         <v>545</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G178" s="5" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="H178" s="5" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="I178" s="4" t="s">
         <v>15</v>
@@ -10201,10 +10270,10 @@
     </row>
     <row r="179" spans="1:10" s="3" customFormat="1" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>1008</v>
+        <v>1001</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>511</v>
@@ -10216,13 +10285,13 @@
         <v>545</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G179" s="5" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="H179" s="5" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="I179" s="4" t="s">
         <v>15</v>
@@ -10231,10 +10300,10 @@
     </row>
     <row r="180" spans="1:10" s="3" customFormat="1" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>511</v>
@@ -10246,13 +10315,13 @@
         <v>545</v>
       </c>
       <c r="F180" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G180" s="5" t="s">
-        <v>1000</v>
+        <v>993</v>
       </c>
       <c r="H180" s="5" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="I180" s="4" t="s">
         <v>15</v>
@@ -10261,10 +10330,10 @@
     </row>
     <row r="181" spans="1:10" s="3" customFormat="1" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>511</v>
@@ -10276,13 +10345,13 @@
         <v>545</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G181" s="5" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="H181" s="5" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="I181" s="4" t="s">
         <v>15</v>
@@ -10291,10 +10360,10 @@
     </row>
     <row r="182" spans="1:10" s="3" customFormat="1" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>1011</v>
+        <v>1004</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>511</v>
@@ -10306,13 +10375,13 @@
         <v>545</v>
       </c>
       <c r="F182" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G182" s="5" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="H182" s="5" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="I182" s="4" t="s">
         <v>15</v>
@@ -10321,10 +10390,10 @@
     </row>
     <row r="183" spans="1:10" s="3" customFormat="1" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>1012</v>
+        <v>1005</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>511</v>
@@ -10336,13 +10405,13 @@
         <v>545</v>
       </c>
       <c r="F183" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G183" s="5" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="H183" s="5" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="I183" s="4" t="s">
         <v>15</v>
@@ -10351,10 +10420,10 @@
     </row>
     <row r="184" spans="1:10" s="3" customFormat="1" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>1013</v>
+        <v>1006</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>511</v>
@@ -10366,13 +10435,13 @@
         <v>545</v>
       </c>
       <c r="F184" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G184" s="5" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="H184" s="5" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="I184" s="4" t="s">
         <v>15</v>
@@ -10381,10 +10450,10 @@
     </row>
     <row r="185" spans="1:10" s="3" customFormat="1" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>1014</v>
+        <v>1007</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>511</v>
@@ -10396,13 +10465,13 @@
         <v>548</v>
       </c>
       <c r="F185" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G185" s="5" t="s">
-        <v>1026</v>
+        <v>1019</v>
       </c>
       <c r="H185" s="5" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="I185" s="4" t="s">
         <v>15</v>
@@ -10411,10 +10480,10 @@
     </row>
     <row r="186" spans="1:10" s="3" customFormat="1" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>1015</v>
+        <v>1008</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>511</v>
@@ -10426,13 +10495,13 @@
         <v>548</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G186" s="5" t="s">
-        <v>1027</v>
+        <v>1020</v>
       </c>
       <c r="H186" s="5" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="I186" s="4" t="s">
         <v>15</v>
@@ -10441,10 +10510,10 @@
     </row>
     <row r="187" spans="1:10" s="3" customFormat="1" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>967</v>
+        <v>962</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>1024</v>
+        <v>1017</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>511</v>
@@ -10456,13 +10525,13 @@
         <v>548</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G187" s="5" t="s">
-        <v>1028</v>
+        <v>1021</v>
       </c>
       <c r="H187" s="5" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="I187" s="4" t="s">
         <v>15</v>
@@ -10471,10 +10540,10 @@
     </row>
     <row r="188" spans="1:10" s="3" customFormat="1" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>1016</v>
+        <v>1009</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>511</v>
@@ -10486,13 +10555,13 @@
         <v>548</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G188" s="5" t="s">
-        <v>1029</v>
+        <v>1022</v>
       </c>
       <c r="H188" s="5" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="I188" s="4" t="s">
         <v>15</v>
@@ -10501,10 +10570,10 @@
     </row>
     <row r="189" spans="1:10" s="3" customFormat="1" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A189" s="4" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>1017</v>
+        <v>1010</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>511</v>
@@ -10516,13 +10585,13 @@
         <v>548</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G189" s="5" t="s">
-        <v>1030</v>
+        <v>1023</v>
       </c>
       <c r="H189" s="5" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="I189" s="4" t="s">
         <v>15</v>
@@ -10531,10 +10600,10 @@
     </row>
     <row r="190" spans="1:10" s="3" customFormat="1" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A190" s="4" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>1018</v>
+        <v>1011</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>511</v>
@@ -10546,13 +10615,13 @@
         <v>548</v>
       </c>
       <c r="F190" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G190" s="5" t="s">
-        <v>1031</v>
+        <v>1024</v>
       </c>
       <c r="H190" s="5" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="I190" s="4" t="s">
         <v>15</v>
@@ -10561,10 +10630,10 @@
     </row>
     <row r="191" spans="1:10" s="3" customFormat="1" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A191" s="4" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>1019</v>
+        <v>1012</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>511</v>
@@ -10576,13 +10645,13 @@
         <v>548</v>
       </c>
       <c r="F191" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G191" s="5" t="s">
-        <v>1032</v>
+        <v>1025</v>
       </c>
       <c r="H191" s="5" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="I191" s="4" t="s">
         <v>15</v>
@@ -10591,10 +10660,10 @@
     </row>
     <row r="192" spans="1:10" s="3" customFormat="1" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A192" s="4" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>1020</v>
+        <v>1013</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>511</v>
@@ -10606,13 +10675,13 @@
         <v>548</v>
       </c>
       <c r="F192" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G192" s="5" t="s">
-        <v>1033</v>
+        <v>1026</v>
       </c>
       <c r="H192" s="5" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="I192" s="4" t="s">
         <v>15</v>
@@ -10621,10 +10690,10 @@
     </row>
     <row r="193" spans="1:10" s="3" customFormat="1" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A193" s="4" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>1021</v>
+        <v>1014</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>511</v>
@@ -10636,13 +10705,13 @@
         <v>548</v>
       </c>
       <c r="F193" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G193" s="5" t="s">
-        <v>1034</v>
+        <v>1027</v>
       </c>
       <c r="H193" s="5" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="I193" s="4" t="s">
         <v>15</v>
@@ -10651,10 +10720,10 @@
     </row>
     <row r="194" spans="1:10" s="3" customFormat="1" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A194" s="4" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>1022</v>
+        <v>1015</v>
       </c>
       <c r="C194" s="4" t="s">
         <v>511</v>
@@ -10666,13 +10735,13 @@
         <v>548</v>
       </c>
       <c r="F194" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G194" s="5" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
       <c r="H194" s="5" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="I194" s="4" t="s">
         <v>15</v>
@@ -10681,10 +10750,10 @@
     </row>
     <row r="195" spans="1:10" s="3" customFormat="1" ht="41.65" x14ac:dyDescent="0.35">
       <c r="A195" s="4" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>1023</v>
+        <v>1016</v>
       </c>
       <c r="C195" s="4" t="s">
         <v>511</v>
@@ -10696,13 +10765,13 @@
         <v>548</v>
       </c>
       <c r="F195" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G195" s="5" t="s">
-        <v>1036</v>
+        <v>1029</v>
       </c>
       <c r="H195" s="5" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="I195" s="4" t="s">
         <v>15</v>
@@ -10711,10 +10780,10 @@
     </row>
     <row r="196" spans="1:10" s="3" customFormat="1" ht="27.75" x14ac:dyDescent="0.35">
       <c r="A196" s="4" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="C196" s="4" t="s">
         <v>511</v>
@@ -10741,10 +10810,10 @@
     </row>
     <row r="197" spans="1:10" s="3" customFormat="1" ht="27.75" x14ac:dyDescent="0.35">
       <c r="A197" s="4" t="s">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="C197" s="4" t="s">
         <v>511</v>
@@ -10756,7 +10825,7 @@
         <v>556</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>1025</v>
+        <v>1018</v>
       </c>
       <c r="G197" s="5" t="s">
         <v>79</v>
@@ -10771,10 +10840,10 @@
     </row>
     <row r="198" spans="1:10" s="3" customFormat="1" ht="55.5" x14ac:dyDescent="0.35">
       <c r="A198" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="B198" s="5" t="s">
         <v>985</v>
-      </c>
-      <c r="B198" s="5" t="s">
-        <v>992</v>
       </c>
       <c r="C198" s="4" t="s">
         <v>511</v>
@@ -10783,16 +10852,16 @@
         <v>20</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>993</v>
+        <v>986</v>
       </c>
       <c r="F198" s="5" t="s">
-        <v>994</v>
+        <v>987</v>
       </c>
       <c r="G198" s="5" t="s">
         <v>79</v>
       </c>
       <c r="H198" s="5" t="s">
-        <v>995</v>
+        <v>988</v>
       </c>
       <c r="I198" s="4" t="s">
         <v>15</v>
@@ -10804,7 +10873,7 @@
         <v>559</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="C199" s="4" t="s">
         <v>560</v>
@@ -10813,16 +10882,16 @@
         <v>71</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>561</v>
+        <v>1042</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="G199" s="5" t="s">
         <v>79</v>
       </c>
       <c r="H199" s="5" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="I199" s="4" t="s">
         <v>15</v>
@@ -10831,10 +10900,10 @@
     </row>
     <row r="200" spans="1:10" s="3" customFormat="1" ht="27.75" x14ac:dyDescent="0.35">
       <c r="A200" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="C200" s="4" t="s">
         <v>560</v>
@@ -10846,48 +10915,192 @@
         <v>144</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G200" s="5" t="s">
         <v>79</v>
       </c>
       <c r="H200" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="I200" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J200" s="5"/>
+    </row>
+    <row r="201" spans="1:10" ht="41.65" x14ac:dyDescent="0.35">
+      <c r="A201" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="I200" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J200" s="5"/>
-    </row>
-    <row r="201" spans="1:10" s="3" customFormat="1" ht="55.5" x14ac:dyDescent="0.35">
-      <c r="A201" s="4" t="s">
-        <v>566</v>
-      </c>
       <c r="B201" s="5" t="s">
-        <v>988</v>
+        <v>1037</v>
       </c>
       <c r="C201" s="4" t="s">
         <v>560</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>71</v>
+        <v>1034</v>
       </c>
       <c r="E201" s="5" t="s">
-        <v>567</v>
+        <v>1043</v>
       </c>
       <c r="F201" s="5" t="s">
-        <v>568</v>
+        <v>1047</v>
       </c>
       <c r="G201" s="5" t="s">
         <v>79</v>
       </c>
       <c r="H201" s="5" t="s">
-        <v>989</v>
+        <v>1050</v>
       </c>
       <c r="I201" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="J201" s="5"/>
+    </row>
+    <row r="202" spans="1:10" ht="27.75" x14ac:dyDescent="0.35">
+      <c r="A202" s="4" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="D202" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E202" s="5" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F202" s="5" t="s">
+        <v>1047</v>
+      </c>
+      <c r="G202" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H202" s="5" t="s">
+        <v>1050</v>
+      </c>
+      <c r="I202" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" ht="27.75" x14ac:dyDescent="0.35">
+      <c r="A203" s="4" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B203" s="5" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C203" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="D203" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E203" s="5" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F203" s="5" t="s">
+        <v>1047</v>
+      </c>
+      <c r="G203" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H203" s="5" t="s">
+        <v>1050</v>
+      </c>
+      <c r="I203" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" ht="41.65" x14ac:dyDescent="0.35">
+      <c r="A204" s="4" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B204" s="5" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="D204" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E204" s="5" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F204" s="5" t="s">
+        <v>1047</v>
+      </c>
+      <c r="G204" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H204" s="5" t="s">
+        <v>1050</v>
+      </c>
+      <c r="I204" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" ht="41.65" x14ac:dyDescent="0.35">
+      <c r="A205" s="4" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C205" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="D205" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E205" s="5" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F205" s="5" t="s">
+        <v>1047</v>
+      </c>
+      <c r="G205" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H205" s="5" t="s">
+        <v>1050</v>
+      </c>
+      <c r="I205" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" ht="41.65" x14ac:dyDescent="0.35">
+      <c r="A206" s="4" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B206" s="5" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="D206" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E206" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F206" s="5" t="s">
+        <v>1047</v>
+      </c>
+      <c r="G206" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H206" s="5" t="s">
+        <v>1050</v>
+      </c>
+      <c r="I206" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
